--- a/results/Int Task Remove ACC 0.8/Rando_10_permute.xlsx
+++ b/results/Int Task Remove ACC 0.8/Rando_10_permute.xlsx
@@ -440,197 +440,197 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4459979494190021</v>
+        <v>0.4426748689906584</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4463727500569606</v>
+        <v>0.4426748689906584</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4460594668489405</v>
+        <v>0.4514411027568923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4493825472772841</v>
+        <v>0.4472453861927546</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4493825472772841</v>
+        <v>0.4583447254499886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4442412850307587</v>
+        <v>0.4647391205285942</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4505069491911597</v>
+        <v>0.4647391205285942</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4505069491911597</v>
+        <v>0.4622943722943723</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.4511335156071998</v>
+        <v>0.4677489177489177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.4500649350649351</v>
+        <v>0.4686272499430394</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4518831168831169</v>
+        <v>0.4686272499430394</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4500649350649351</v>
+        <v>0.4676874003189793</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4676874003189793</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.4676874003189793</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4555137844611529</v>
+        <v>0.4670608339029392</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4555137844611529</v>
+        <v>0.4761517429938483</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4467418546365915</v>
+        <v>0.4761517429938483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4420426065162907</v>
+        <v>0.4761517429938483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4423558897243108</v>
+        <v>0.4761517429938483</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4423558897243108</v>
+        <v>0.4801013898382319</v>
       </c>
     </row>
     <row r="22">
@@ -640,687 +640,687 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4467418546365915</v>
+        <v>0.4810412394622921</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4467418546365915</v>
+        <v>0.500291638186375</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4489348370927319</v>
+        <v>0.5054329004329005</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4492481203007519</v>
+        <v>0.5211699703804967</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4492481203007519</v>
+        <v>0.5096958304853042</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4520676691729323</v>
+        <v>0.5182216905901117</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4526942355889724</v>
+        <v>0.5175951241740715</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4526942355889724</v>
+        <v>0.4821041239462293</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4617794486215539</v>
+        <v>0.4797208931419458</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4614661654135339</v>
+        <v>0.478215994531784</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4614661654135339</v>
+        <v>0.4800341763499658</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4614661654135339</v>
+        <v>0.4948929141034404</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4611528822055138</v>
+        <v>0.4879949874686716</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4611528822055138</v>
+        <v>0.4726384142173616</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4611528822055138</v>
+        <v>0.4756482114376851</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4724310776942356</v>
+        <v>0.4756482114376851</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4733709273182957</v>
+        <v>0.4930132148553201</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.468671679197995</v>
+        <v>0.4930132148553201</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.468671679197995</v>
+        <v>0.4883754841649578</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.468671679197995</v>
+        <v>0.4883754841649578</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.468671679197995</v>
+        <v>0.543485987696514</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.468671679197995</v>
+        <v>0.5133264980633402</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4696115288220551</v>
+        <v>0.6175279106858054</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4696115288220551</v>
+        <v>0.5950831624515835</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4696115288220551</v>
+        <v>0.5995978582820688</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4683583959899749</v>
+        <v>0.5132649806334016</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.468671679197995</v>
+        <v>0.466680337206653</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4698632946001367</v>
+        <v>0.4673069036226931</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4692367281840966</v>
+        <v>0.4600341763499658</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4902882205513784</v>
+        <v>0.4523809523809524</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4896616541353384</v>
+        <v>0.4533208020050125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.4614046479835954</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4949874686716792</v>
+        <v>0.4689906584643427</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.4677990430622009</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4940476190476191</v>
+        <v>0.4649794941900205</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4926714513556619</v>
+        <v>0.4740704032809296</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4926714513556619</v>
+        <v>0.4848507632718159</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.49053998632946</v>
+        <v>0.4842241968557758</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.49053998632946</v>
+        <v>0.4978913192071087</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4877204374572796</v>
+        <v>0.4999555707450444</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4901651856915015</v>
+        <v>0.5134381408065618</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4948644338118022</v>
+        <v>0.5134381408065618</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4963078149920255</v>
+        <v>0.4923695602642971</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4922966507177033</v>
+        <v>0.4981373889268626</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4860309865573023</v>
+        <v>0.4981373889268626</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4805149236728184</v>
+        <v>0.5090464798359535</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4823946229209387</v>
+        <v>0.5010241512873093</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4789485076327182</v>
+        <v>0.5177010708589657</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4788869902027797</v>
+        <v>0.5177010708589657</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4647334244702666</v>
+        <v>0.5708088402825245</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.470557074504443</v>
+        <v>0.6101936659831396</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.451637047163363</v>
+        <v>0.5760230120756437</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.451637047163363</v>
+        <v>0.4868534973798131</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4494440647072226</v>
+        <v>0.4906687172476646</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4671895648211438</v>
+        <v>0.5001344269765322</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4671895648211438</v>
+        <v>0.5349988607883345</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4605491000227843</v>
+        <v>0.5341205285942128</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4544178628389154</v>
+        <v>0.5152506265664161</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4813328776486672</v>
+        <v>0.520330371383003</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4575461380724539</v>
+        <v>0.5336283891547049</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4721029847345637</v>
+        <v>0.5241797676008202</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4717897015265436</v>
+        <v>0.5427477785372522</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4724834814308498</v>
+        <v>0.5271508316245158</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4548564593301435</v>
+        <v>0.4941011619958988</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.451058327637275</v>
+        <v>0.4930382775119617</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.451058327637275</v>
+        <v>0.4772510822510823</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4506607427660059</v>
+        <v>0.4785657325131009</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4743483709273183</v>
+        <v>0.4781909318751424</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4737218045112782</v>
+        <v>0.4805354294827979</v>
       </c>
     </row>
   </sheetData>
